--- a/Employee_Reports_wi52/Shanel Rukshan Perera Kurana Patabendige Q0628.xlsx
+++ b/Employee_Reports_wi52/Shanel Rukshan Perera Kurana Patabendige Q0628.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,6 +84,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -560,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1148,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1185,11 +1194,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1234,11 +1243,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1284,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1333,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1382,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1431,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1480,11 +1489,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1529,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1566,11 +1575,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1603,11 +1612,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1652,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1665,6 +1674,43 @@
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1680,15 +1726,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
     <col width="2" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1764,52 +1810,83 @@
       <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Consignment Shuttle Tv</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>73.59%</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>low percentage</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Turntable &amp; Ra Deck</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>30-Jul-2026</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>76.32%</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>77.53%</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>76.22%</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1897,7 +1974,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1992,7 +2069,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2021,7 +2098,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2050,7 +2127,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2079,7 +2156,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2108,7 +2185,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2214,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2166,7 +2243,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2195,7 +2272,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2224,7 +2301,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2253,7 +2330,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2282,7 +2359,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2311,7 +2388,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2417,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2446,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2398,7 +2475,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2427,7 +2504,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2456,7 +2533,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2485,7 +2562,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2514,7 +2591,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2543,7 +2620,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2572,7 +2649,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
